--- a/Datasources/Wires.xlsx
+++ b/Datasources/Wires.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Inductor Design\Datasources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47042861-0825-4179-BD33-D26E5C539F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5C6A5-1A08-4BC3-B258-83AD366539E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{4BB6EF32-6047-4CBB-A83F-F4A6A23D553A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Wires" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="128">
   <si>
     <t>Strands</t>
   </si>
@@ -57,23 +58,379 @@
   </si>
   <si>
     <t>Custom</t>
+  </si>
+  <si>
+    <t>1x AWG 10</t>
+  </si>
+  <si>
+    <t>1x AWG 11</t>
+  </si>
+  <si>
+    <t>1x AWG 12</t>
+  </si>
+  <si>
+    <t>1x AWG 13</t>
+  </si>
+  <si>
+    <t>1x AWG 14</t>
+  </si>
+  <si>
+    <t>1x AWG 15</t>
+  </si>
+  <si>
+    <t>1x AWG 16</t>
+  </si>
+  <si>
+    <t>1x AWG 17</t>
+  </si>
+  <si>
+    <t>1x AWG 18</t>
+  </si>
+  <si>
+    <t>1x AWG 19</t>
+  </si>
+  <si>
+    <t>1x AWG 20</t>
+  </si>
+  <si>
+    <t>1x AWG 21</t>
+  </si>
+  <si>
+    <t>1x AWG 22</t>
+  </si>
+  <si>
+    <t>1x AWG 23</t>
+  </si>
+  <si>
+    <t>1x AWG 24</t>
+  </si>
+  <si>
+    <t>1x AWG 25</t>
+  </si>
+  <si>
+    <t>1x AWG 26</t>
+  </si>
+  <si>
+    <t>1x AWG 27</t>
+  </si>
+  <si>
+    <t>1x AWG 28</t>
+  </si>
+  <si>
+    <t>1x AWG 29</t>
+  </si>
+  <si>
+    <t>1x AWG 30</t>
+  </si>
+  <si>
+    <t>1x AWG 31</t>
+  </si>
+  <si>
+    <t>1x AWG 32</t>
+  </si>
+  <si>
+    <t>1x AWG 33</t>
+  </si>
+  <si>
+    <t>1x AWG 34</t>
+  </si>
+  <si>
+    <t>3x AWG 34</t>
+  </si>
+  <si>
+    <t>4x AWG 34</t>
+  </si>
+  <si>
+    <t>5x AWG 34</t>
+  </si>
+  <si>
+    <t>6x AWG 34</t>
+  </si>
+  <si>
+    <t>7x AWG 34</t>
+  </si>
+  <si>
+    <t>8x AWG 34</t>
+  </si>
+  <si>
+    <t>9x AWG 34</t>
+  </si>
+  <si>
+    <t>10x AWG 34</t>
+  </si>
+  <si>
+    <t>15x AWG 34</t>
+  </si>
+  <si>
+    <t>20x AWG 34</t>
+  </si>
+  <si>
+    <t>1x AWG 35</t>
+  </si>
+  <si>
+    <t>1x AWG 36</t>
+  </si>
+  <si>
+    <t>1x AWG 37</t>
+  </si>
+  <si>
+    <t>1x AWG 38</t>
+  </si>
+  <si>
+    <t>2x AWG 38</t>
+  </si>
+  <si>
+    <t>3x AWG 38</t>
+  </si>
+  <si>
+    <t>4x AWG 38</t>
+  </si>
+  <si>
+    <t>5x AWG 38</t>
+  </si>
+  <si>
+    <t>6x AWG 38</t>
+  </si>
+  <si>
+    <t>7x AWG 38</t>
+  </si>
+  <si>
+    <t>8x AWG 38</t>
+  </si>
+  <si>
+    <t>9x AWG 38</t>
+  </si>
+  <si>
+    <t>10x AWG 38</t>
+  </si>
+  <si>
+    <t>15x AWG 38</t>
+  </si>
+  <si>
+    <t>20x AWG 38</t>
+  </si>
+  <si>
+    <t>25x AWG 38</t>
+  </si>
+  <si>
+    <t>30x AWG 38</t>
+  </si>
+  <si>
+    <t>40x AWG 38</t>
+  </si>
+  <si>
+    <t>50x AWG 38</t>
+  </si>
+  <si>
+    <t>60x AWG 38</t>
+  </si>
+  <si>
+    <t>1x AWG 39</t>
+  </si>
+  <si>
+    <t>1x AWG 40</t>
+  </si>
+  <si>
+    <t>1x AWG 41</t>
+  </si>
+  <si>
+    <t>2x AWG 27</t>
+  </si>
+  <si>
+    <t>3x AWG 27</t>
+  </si>
+  <si>
+    <t>4x AWG 27</t>
+  </si>
+  <si>
+    <t>5x AWG 27</t>
+  </si>
+  <si>
+    <t>6x AWG 27</t>
+  </si>
+  <si>
+    <t>7x AWG 27</t>
+  </si>
+  <si>
+    <t>8x AWG 27</t>
+  </si>
+  <si>
+    <t>9x AWG 27</t>
+  </si>
+  <si>
+    <t>10x AWG 27</t>
+  </si>
+  <si>
+    <t>2x AWG 28</t>
+  </si>
+  <si>
+    <t>3x AWG 28</t>
+  </si>
+  <si>
+    <t>4x AWG 28</t>
+  </si>
+  <si>
+    <t>5x AWG 28</t>
+  </si>
+  <si>
+    <t>6x AWG 28</t>
+  </si>
+  <si>
+    <t>7x AWG 28</t>
+  </si>
+  <si>
+    <t>8x AWG 28</t>
+  </si>
+  <si>
+    <t>9x AWG 28</t>
+  </si>
+  <si>
+    <t>10x AWG 28</t>
+  </si>
+  <si>
+    <t>2x AWG 26</t>
+  </si>
+  <si>
+    <t>3x AWG 26</t>
+  </si>
+  <si>
+    <t>4x AWG 26</t>
+  </si>
+  <si>
+    <t>5x AWG 26</t>
+  </si>
+  <si>
+    <t>6x AWG 26</t>
+  </si>
+  <si>
+    <t>7x AWG 26</t>
+  </si>
+  <si>
+    <t>8x AWG 26</t>
+  </si>
+  <si>
+    <t>9x AWG 26</t>
+  </si>
+  <si>
+    <t>10x AWG 26</t>
+  </si>
+  <si>
+    <t>2x AWG 23</t>
+  </si>
+  <si>
+    <t>3x AWG 23</t>
+  </si>
+  <si>
+    <t>4x AWG 23</t>
+  </si>
+  <si>
+    <t>5x AWG 23</t>
+  </si>
+  <si>
+    <t>6x AWG 23</t>
+  </si>
+  <si>
+    <t>7x AWG 23</t>
+  </si>
+  <si>
+    <t>8x AWG 23</t>
+  </si>
+  <si>
+    <t>9x AWG 23</t>
+  </si>
+  <si>
+    <t>10x AWG 23</t>
+  </si>
+  <si>
+    <t>2x AWG 24</t>
+  </si>
+  <si>
+    <t>3x AWG 24</t>
+  </si>
+  <si>
+    <t>4x AWG 24</t>
+  </si>
+  <si>
+    <t>5x AWG 24</t>
+  </si>
+  <si>
+    <t>6x AWG 24</t>
+  </si>
+  <si>
+    <t>7x AWG 24</t>
+  </si>
+  <si>
+    <t>8x AWG 24</t>
+  </si>
+  <si>
+    <t>9x AWG 24</t>
+  </si>
+  <si>
+    <t>10x AWG 24</t>
+  </si>
+  <si>
+    <t>2x AWG 25</t>
+  </si>
+  <si>
+    <t>3x AWG 25</t>
+  </si>
+  <si>
+    <t>4x AWG 25</t>
+  </si>
+  <si>
+    <t>5x AWG 25</t>
+  </si>
+  <si>
+    <t>6x AWG 25</t>
+  </si>
+  <si>
+    <t>7x AWG 25</t>
+  </si>
+  <si>
+    <t>8x AWG 25</t>
+  </si>
+  <si>
+    <t>9x AWG 25</t>
+  </si>
+  <si>
+    <t>10x AWG 25</t>
+  </si>
+  <si>
+    <t>2x AWG 22</t>
+  </si>
+  <si>
+    <t>3x AWG 22</t>
+  </si>
+  <si>
+    <t>4x AWG 22</t>
+  </si>
+  <si>
+    <t>5x AWG 22</t>
+  </si>
+  <si>
+    <t>6x AWG 22</t>
+  </si>
+  <si>
+    <t>7x AWG 22</t>
+  </si>
+  <si>
+    <t>8x AWG 22</t>
+  </si>
+  <si>
+    <t>9x AWG 22</t>
+  </si>
+  <si>
+    <t>10x AWG 22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -99,9 +456,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -118,25 +474,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE3D3767-259A-42C2-9C0F-A45257BA2769}" name="Table1" displayName="Table1" ref="A1:G1048575" totalsRowShown="0">
-  <autoFilter ref="A1:G1048575" xr:uid="{BE3D3767-259A-42C2-9C0F-A45257BA2769}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G1048575">
-    <sortCondition ref="C1:C1048575"/>
-  </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C70D3467-FA8E-4901-B60A-2DA7BD6B22C2}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{AE954433-D445-4615-945C-49059CB63C21}" name="Strands"/>
-    <tableColumn id="3" xr3:uid="{BC550C86-57F7-4983-85EF-F59FEFA7B0B0}" name="AWG"/>
-    <tableColumn id="4" xr3:uid="{8867997C-A0B2-4809-8370-713DC36B4699}" name="S_Cu"/>
-    <tableColumn id="5" xr3:uid="{BD20723F-E294-4D6F-80D1-84FD1B70628B}" name="S_Total"/>
-    <tableColumn id="6" xr3:uid="{6F4299E6-0DB4-4A88-B102-2345233CDA0E}" name="Ohm_m"/>
-    <tableColumn id="7" xr3:uid="{FC7272AF-661A-45EE-B6D8-40BA9EE51F8A}" name="Custom"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,16 +772,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F767DF1-5E83-4FC3-B5A6-8655037DF642}">
-  <dimension ref="A1:G59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8903D472-F721-4166-9A47-1F6CC7955A0E}">
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -471,9 +807,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="str">
-        <f>CONCATENATE(B2,"x AWG ",C2)</f>
-        <v>1x AWG 10</v>
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -481,10 +816,10 @@
       <c r="C2">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>5.2619999999999998E-6</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>5.8571999999999996E-6</v>
       </c>
       <c r="F2">
@@ -495,9 +830,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="str">
-        <f>CONCATENATE(B3,"x AWG ",C3)</f>
-        <v>1x AWG 11</v>
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -505,10 +839,10 @@
       <c r="C3">
         <v>11</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>4.1729000000000003E-6</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>4.6738E-6</v>
       </c>
       <c r="F3">
@@ -519,9 +853,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="str">
-        <f>CONCATENATE(B4,"x AWG ",C4)</f>
-        <v>1x AWG 12</v>
+      <c r="A4" t="s">
+        <v>9</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -529,10 +862,10 @@
       <c r="C4">
         <v>12</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>3.3092E-6</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>3.7309000000000001E-6</v>
       </c>
       <c r="F4">
@@ -543,9 +876,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="str">
-        <f>CONCATENATE(B5,"x AWG ",C5)</f>
-        <v>1x AWG 13</v>
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -553,10 +885,10 @@
       <c r="C5">
         <v>13</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>2.6243E-6</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>2.9793E-6</v>
       </c>
       <c r="F5">
@@ -567,9 +899,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="str">
-        <f>CONCATENATE(B6,"x AWG ",C6)</f>
-        <v>1x AWG 14</v>
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -577,10 +908,10 @@
       <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>2.0810999999999999E-6</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>2.3800000000000001E-6</v>
       </c>
       <c r="F6">
@@ -591,9 +922,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="str">
-        <f>CONCATENATE(B7,"x AWG ",C7)</f>
-        <v>1x AWG 15</v>
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -601,10 +931,10 @@
       <c r="C7">
         <v>15</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>1.6503999999999999E-6</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>1.9021E-6</v>
       </c>
       <c r="F7">
@@ -615,9 +945,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="str">
-        <f>CONCATENATE(B8,"x AWG ",C8)</f>
-        <v>1x AWG 16</v>
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -625,10 +954,10 @@
       <c r="C8">
         <v>16</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>1.3088000000000001E-6</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>1.5206999999999999E-6</v>
       </c>
       <c r="F8">
@@ -639,9 +968,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="str">
-        <f>CONCATENATE(B9,"x AWG ",C9)</f>
-        <v>1x AWG 17</v>
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -649,10 +977,10 @@
       <c r="C9">
         <v>17</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>1.0379E-6</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>1.2163999999999999E-6</v>
       </c>
       <c r="F9">
@@ -663,9 +991,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="str">
-        <f>CONCATENATE(B10,"x AWG ",C10)</f>
-        <v>1x AWG 18</v>
+      <c r="A10" t="s">
+        <v>15</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -673,10 +1000,10 @@
       <c r="C10">
         <v>18</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>8.2310000000000001E-7</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
         <v>9.7350000000000008E-7</v>
       </c>
       <c r="F10">
@@ -687,9 +1014,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="str">
-        <f>CONCATENATE(B11,"x AWG ",C11)</f>
-        <v>1x AWG 19</v>
+      <c r="A11" t="s">
+        <v>16</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -697,10 +1023,10 @@
       <c r="C11">
         <v>19</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>6.5270000000000001E-7</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
         <v>7.794E-7</v>
       </c>
       <c r="F11">
@@ -711,9 +1037,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="str">
-        <f>CONCATENATE(B12,"x AWG ",C12)</f>
-        <v>1x AWG 20</v>
+      <c r="A12" t="s">
+        <v>17</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -721,10 +1046,10 @@
       <c r="C12">
         <v>20</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>5.1760000000000003E-7</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>6.2440000000000001E-7</v>
       </c>
       <c r="F12">
@@ -735,9 +1060,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="str">
-        <f>CONCATENATE(B13,"x AWG ",C13)</f>
-        <v>1x AWG 21</v>
+      <c r="A13" t="s">
+        <v>18</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -745,10 +1069,10 @@
       <c r="C13">
         <v>21</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>4.1049999999999998E-7</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13">
         <v>5.0040000000000001E-7</v>
       </c>
       <c r="F13">
@@ -759,9 +1083,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="str">
-        <f>CONCATENATE(B14,"x AWG ",C14)</f>
-        <v>1x AWG 22</v>
+      <c r="A14" t="s">
+        <v>19</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -769,10 +1092,10 @@
       <c r="C14">
         <v>22</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>3.255E-7</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14">
         <v>4.0129999999999997E-7</v>
       </c>
       <c r="F14">
@@ -783,1089 +1106,2778 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="str">
-        <f>CONCATENATE(B15,"x AWG ",C15)</f>
-        <v>1x AWG 23</v>
+      <c r="A15" t="s">
+        <v>119</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>6.5099999999999999E-7</v>
+      </c>
+      <c r="E15">
+        <v>8.0259999999999995E-7</v>
+      </c>
+      <c r="F15">
+        <v>2.6469599999999999E-2</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>22</v>
+      </c>
+      <c r="D16">
+        <v>9.7649999999999988E-7</v>
+      </c>
+      <c r="E16">
+        <v>1.2039E-6</v>
+      </c>
+      <c r="F16">
+        <v>1.76464E-2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>22</v>
+      </c>
+      <c r="D17">
+        <v>1.302E-6</v>
+      </c>
+      <c r="E17">
+        <v>1.6051999999999999E-6</v>
+      </c>
+      <c r="F17">
+        <v>1.32348E-2</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>22</v>
+      </c>
+      <c r="D18">
+        <v>1.6275000000000001E-6</v>
+      </c>
+      <c r="E18">
+        <v>2.0064999999999998E-6</v>
+      </c>
+      <c r="F18">
+        <v>1.0587839999999999E-2</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>22</v>
+      </c>
+      <c r="D19">
+        <v>1.9529999999999998E-6</v>
+      </c>
+      <c r="E19">
+        <v>2.4078000000000001E-6</v>
+      </c>
+      <c r="F19">
+        <v>8.8231999999999998E-3</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>22</v>
+      </c>
+      <c r="D20">
+        <v>2.2784999999999999E-6</v>
+      </c>
+      <c r="E20">
+        <v>2.8090999999999999E-6</v>
+      </c>
+      <c r="F20">
+        <v>7.5627428571428566E-3</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>22</v>
+      </c>
+      <c r="D21">
+        <v>2.604E-6</v>
+      </c>
+      <c r="E21">
+        <v>3.2103999999999998E-6</v>
+      </c>
+      <c r="F21">
+        <v>6.6173999999999998E-3</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>2.9295000000000001E-6</v>
+      </c>
+      <c r="E22">
+        <v>3.6116999999999997E-6</v>
+      </c>
+      <c r="F22">
+        <v>5.8821333333333335E-3</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <v>3.2550000000000002E-6</v>
+      </c>
+      <c r="E23">
+        <v>4.0129999999999995E-6</v>
+      </c>
+      <c r="F23">
+        <v>5.2939199999999997E-3</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
         <v>23</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D24">
         <v>2.5820000000000002E-7</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E24">
         <v>3.2210000000000001E-7</v>
       </c>
-      <c r="F15">
+      <c r="F24">
         <v>6.6780800000000001E-2</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="str">
-        <f>CONCATENATE(B16,"x AWG ",C16)</f>
-        <v>1x AWG 24</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>5.1640000000000004E-7</v>
+      </c>
+      <c r="E25">
+        <v>6.4420000000000001E-7</v>
+      </c>
+      <c r="F25">
+        <v>3.3390400000000001E-2</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>23</v>
+      </c>
+      <c r="D26">
+        <v>7.7460000000000007E-7</v>
+      </c>
+      <c r="E26">
+        <v>9.6629999999999996E-7</v>
+      </c>
+      <c r="F26">
+        <v>2.2260266666666667E-2</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>23</v>
+      </c>
+      <c r="D27">
+        <v>1.0328000000000001E-6</v>
+      </c>
+      <c r="E27">
+        <v>1.2884E-6</v>
+      </c>
+      <c r="F27">
+        <v>1.66952E-2</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>1.291E-6</v>
+      </c>
+      <c r="E28">
+        <v>1.6105000000000001E-6</v>
+      </c>
+      <c r="F28">
+        <v>1.3356160000000001E-2</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>1.5492000000000001E-6</v>
+      </c>
+      <c r="E29">
+        <v>1.9325999999999999E-6</v>
+      </c>
+      <c r="F29">
+        <v>1.1130133333333334E-2</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>23</v>
+      </c>
+      <c r="D30">
+        <v>1.8074000000000003E-6</v>
+      </c>
+      <c r="E30">
+        <v>2.2547000000000002E-6</v>
+      </c>
+      <c r="F30">
+        <v>9.5401142857142861E-3</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>23</v>
+      </c>
+      <c r="D31">
+        <v>2.0656000000000002E-6</v>
+      </c>
+      <c r="E31">
+        <v>2.5768E-6</v>
+      </c>
+      <c r="F31">
+        <v>8.3476000000000002E-3</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>2.3238000000000001E-6</v>
+      </c>
+      <c r="E32">
+        <v>2.8988999999999999E-6</v>
+      </c>
+      <c r="F32">
+        <v>7.4200888888888887E-3</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>23</v>
+      </c>
+      <c r="D33">
+        <v>2.582E-6</v>
+      </c>
+      <c r="E33">
+        <v>3.2210000000000002E-6</v>
+      </c>
+      <c r="F33">
+        <v>6.6780800000000003E-3</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
         <v>24</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D34">
         <v>2.047E-7</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E34">
         <v>2.586E-7</v>
       </c>
-      <c r="F16">
+      <c r="F34">
         <v>8.4197599999999997E-2</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="str">
-        <f>CONCATENATE(B17,"x AWG ",C17)</f>
-        <v>1x AWG 25</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>24</v>
+      </c>
+      <c r="D35">
+        <v>4.094E-7</v>
+      </c>
+      <c r="E35">
+        <v>5.172E-7</v>
+      </c>
+      <c r="F35">
+        <v>4.2098799999999999E-2</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>24</v>
+      </c>
+      <c r="D36">
+        <v>6.1409999999999997E-7</v>
+      </c>
+      <c r="E36">
+        <v>7.7580000000000005E-7</v>
+      </c>
+      <c r="F36">
+        <v>2.8065866666666665E-2</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>8.188E-7</v>
+      </c>
+      <c r="E37">
+        <v>1.0344E-6</v>
+      </c>
+      <c r="F37">
+        <v>2.1049399999999999E-2</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>24</v>
+      </c>
+      <c r="D38">
+        <v>1.0235E-6</v>
+      </c>
+      <c r="E38">
+        <v>1.2929999999999999E-6</v>
+      </c>
+      <c r="F38">
+        <v>1.683952E-2</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>24</v>
+      </c>
+      <c r="D39">
+        <v>1.2281999999999999E-6</v>
+      </c>
+      <c r="E39">
+        <v>1.5516000000000001E-6</v>
+      </c>
+      <c r="F39">
+        <v>1.4032933333333332E-2</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>24</v>
+      </c>
+      <c r="D40">
+        <v>1.4329000000000001E-6</v>
+      </c>
+      <c r="E40">
+        <v>1.8102E-6</v>
+      </c>
+      <c r="F40">
+        <v>1.2028228571428571E-2</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>24</v>
+      </c>
+      <c r="D41">
+        <v>1.6376E-6</v>
+      </c>
+      <c r="E41">
+        <v>2.0688E-6</v>
+      </c>
+      <c r="F41">
+        <v>1.05247E-2</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>24</v>
+      </c>
+      <c r="D42">
+        <v>1.8422999999999999E-6</v>
+      </c>
+      <c r="E42">
+        <v>2.3273999999999999E-6</v>
+      </c>
+      <c r="F42">
+        <v>9.3552888888888894E-3</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>24</v>
+      </c>
+      <c r="D43">
+        <v>2.0470000000000001E-6</v>
+      </c>
+      <c r="E43">
+        <v>2.5859999999999999E-6</v>
+      </c>
+      <c r="F43">
+        <v>8.4197600000000001E-3</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
         <v>25</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D44">
         <v>1.624E-7</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E44">
         <v>2.0779999999999999E-7</v>
       </c>
-      <c r="F17">
+      <c r="F44">
         <v>0.10617360000000001</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="str">
-        <f>CONCATENATE(B18,"x AWG ",C18)</f>
-        <v>1x AWG 26</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>25</v>
+      </c>
+      <c r="D45">
+        <v>3.248E-7</v>
+      </c>
+      <c r="E45">
+        <v>4.1559999999999999E-7</v>
+      </c>
+      <c r="F45">
+        <v>5.3086800000000003E-2</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46">
+        <v>25</v>
+      </c>
+      <c r="D46">
+        <v>4.8719999999999997E-7</v>
+      </c>
+      <c r="E46">
+        <v>6.2340000000000004E-7</v>
+      </c>
+      <c r="F46">
+        <v>3.5391200000000005E-2</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>25</v>
+      </c>
+      <c r="D47">
+        <v>6.4959999999999999E-7</v>
+      </c>
+      <c r="E47">
+        <v>8.3119999999999998E-7</v>
+      </c>
+      <c r="F47">
+        <v>2.6543400000000002E-2</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48">
+        <v>25</v>
+      </c>
+      <c r="D48">
+        <v>8.1200000000000002E-7</v>
+      </c>
+      <c r="E48">
+        <v>1.0389999999999999E-6</v>
+      </c>
+      <c r="F48">
+        <v>2.1234720000000002E-2</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>9.7439999999999994E-7</v>
+      </c>
+      <c r="E49">
+        <v>1.2468000000000001E-6</v>
+      </c>
+      <c r="F49">
+        <v>1.7695600000000002E-2</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>1.1368000000000001E-6</v>
+      </c>
+      <c r="E50">
+        <v>1.4546E-6</v>
+      </c>
+      <c r="F50">
+        <v>1.5167657142857144E-2</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>25</v>
+      </c>
+      <c r="D51">
+        <v>1.2992E-6</v>
+      </c>
+      <c r="E51">
+        <v>1.6624E-6</v>
+      </c>
+      <c r="F51">
+        <v>1.3271700000000001E-2</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>25</v>
+      </c>
+      <c r="D52">
+        <v>1.4615999999999999E-6</v>
+      </c>
+      <c r="E52">
+        <v>1.8701999999999999E-6</v>
+      </c>
+      <c r="F52">
+        <v>1.1797066666666668E-2</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>1.624E-6</v>
+      </c>
+      <c r="E53">
+        <v>2.0779999999999998E-6</v>
+      </c>
+      <c r="F53">
+        <v>1.0617360000000001E-2</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
         <v>26</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D54">
         <v>1.2870000000000001E-7</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E54">
         <v>1.6710000000000001E-7</v>
       </c>
-      <c r="F18">
+      <c r="F54">
         <v>0.1338568</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="str">
-        <f>CONCATENATE(B19,"x AWG ",C19)</f>
-        <v>1x AWG 27</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>26</v>
+      </c>
+      <c r="D55">
+        <v>2.5740000000000002E-7</v>
+      </c>
+      <c r="E55">
+        <v>3.3420000000000001E-7</v>
+      </c>
+      <c r="F55">
+        <v>6.6928399999999999E-2</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56">
+        <v>26</v>
+      </c>
+      <c r="D56">
+        <v>3.861E-7</v>
+      </c>
+      <c r="E56">
+        <v>5.0129999999999997E-7</v>
+      </c>
+      <c r="F56">
+        <v>4.4618933333333333E-2</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>26</v>
+      </c>
+      <c r="D57">
+        <v>5.1480000000000003E-7</v>
+      </c>
+      <c r="E57">
+        <v>6.6840000000000003E-7</v>
+      </c>
+      <c r="F57">
+        <v>3.34642E-2</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58">
+        <v>26</v>
+      </c>
+      <c r="D58">
+        <v>6.4350000000000006E-7</v>
+      </c>
+      <c r="E58">
+        <v>8.3550000000000009E-7</v>
+      </c>
+      <c r="F58">
+        <v>2.6771360000000001E-2</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>26</v>
+      </c>
+      <c r="D59">
+        <v>7.7219999999999999E-7</v>
+      </c>
+      <c r="E59">
+        <v>1.0025999999999999E-6</v>
+      </c>
+      <c r="F59">
+        <v>2.2309466666666666E-2</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>26</v>
+      </c>
+      <c r="D60">
+        <v>9.0090000000000003E-7</v>
+      </c>
+      <c r="E60">
+        <v>1.1697E-6</v>
+      </c>
+      <c r="F60">
+        <v>1.9122400000000001E-2</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>26</v>
+      </c>
+      <c r="D61">
+        <v>1.0296000000000001E-6</v>
+      </c>
+      <c r="E61">
+        <v>1.3368000000000001E-6</v>
+      </c>
+      <c r="F61">
+        <v>1.67321E-2</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62">
+        <v>26</v>
+      </c>
+      <c r="D62">
+        <v>1.1583E-6</v>
+      </c>
+      <c r="E62">
+        <v>1.5039000000000001E-6</v>
+      </c>
+      <c r="F62">
+        <v>1.4872977777777777E-2</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>26</v>
+      </c>
+      <c r="D63">
+        <v>1.2870000000000001E-6</v>
+      </c>
+      <c r="E63">
+        <v>1.6710000000000002E-6</v>
+      </c>
+      <c r="F63">
+        <v>1.338568E-2</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
         <v>27</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D64">
         <v>1.0209999999999999E-7</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E64">
         <v>1.3440000000000001E-7</v>
       </c>
-      <c r="F19">
+      <c r="F64">
         <v>0.16882159999999999</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" t="str">
-        <f>CONCATENATE(B20,"x AWG ",C20)</f>
-        <v>1x AWG 28</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
+      <c r="G64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>27</v>
+      </c>
+      <c r="D65">
+        <v>2.0419999999999999E-7</v>
+      </c>
+      <c r="E65">
+        <v>2.6880000000000002E-7</v>
+      </c>
+      <c r="F65">
+        <v>8.4410799999999994E-2</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66">
+        <v>27</v>
+      </c>
+      <c r="D66">
+        <v>3.0629999999999998E-7</v>
+      </c>
+      <c r="E66">
+        <v>4.0320000000000001E-7</v>
+      </c>
+      <c r="F66">
+        <v>5.6273866666666665E-2</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>27</v>
+      </c>
+      <c r="D67">
+        <v>4.0839999999999998E-7</v>
+      </c>
+      <c r="E67">
+        <v>5.3760000000000005E-7</v>
+      </c>
+      <c r="F67">
+        <v>4.2205399999999997E-2</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68">
+        <v>27</v>
+      </c>
+      <c r="D68">
+        <v>5.1050000000000003E-7</v>
+      </c>
+      <c r="E68">
+        <v>6.7200000000000009E-7</v>
+      </c>
+      <c r="F68">
+        <v>3.376432E-2</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
+      </c>
+      <c r="C69">
+        <v>27</v>
+      </c>
+      <c r="D69">
+        <v>6.1259999999999997E-7</v>
+      </c>
+      <c r="E69">
+        <v>8.0640000000000002E-7</v>
+      </c>
+      <c r="F69">
+        <v>2.8136933333333333E-2</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>27</v>
+      </c>
+      <c r="D70">
+        <v>7.1469999999999991E-7</v>
+      </c>
+      <c r="E70">
+        <v>9.4080000000000006E-7</v>
+      </c>
+      <c r="F70">
+        <v>2.4117371428571427E-2</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71">
+        <v>8</v>
+      </c>
+      <c r="C71">
+        <v>27</v>
+      </c>
+      <c r="D71">
+        <v>8.1679999999999996E-7</v>
+      </c>
+      <c r="E71">
+        <v>1.0752000000000001E-6</v>
+      </c>
+      <c r="F71">
+        <v>2.1102699999999999E-2</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>27</v>
+      </c>
+      <c r="D72">
+        <v>9.189E-7</v>
+      </c>
+      <c r="E72">
+        <v>1.2096E-6</v>
+      </c>
+      <c r="F72">
+        <v>1.8757955555555553E-2</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73">
+        <v>10</v>
+      </c>
+      <c r="C73">
+        <v>27</v>
+      </c>
+      <c r="D73">
+        <v>1.0210000000000001E-6</v>
+      </c>
+      <c r="E73">
+        <v>1.3440000000000002E-6</v>
+      </c>
+      <c r="F73">
+        <v>1.688216E-2</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
         <v>28</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D74">
         <v>8.0999999999999997E-8</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E74">
         <v>1.083E-7</v>
       </c>
-      <c r="F20">
+      <c r="F74">
         <v>0.21287200000000001</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="str">
-        <f>CONCATENATE(B21,"x AWG ",C21)</f>
-        <v>1x AWG 29</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
+      <c r="G74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>28</v>
+      </c>
+      <c r="D75">
+        <v>1.6199999999999999E-7</v>
+      </c>
+      <c r="E75">
+        <v>2.1659999999999999E-7</v>
+      </c>
+      <c r="F75">
+        <v>0.106436</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76">
+        <v>28</v>
+      </c>
+      <c r="D76">
+        <v>2.4299999999999999E-7</v>
+      </c>
+      <c r="E76">
+        <v>3.249E-7</v>
+      </c>
+      <c r="F76">
+        <v>7.0957333333333331E-2</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>28</v>
+      </c>
+      <c r="D77">
+        <v>3.2399999999999999E-7</v>
+      </c>
+      <c r="E77">
+        <v>4.3319999999999999E-7</v>
+      </c>
+      <c r="F77">
+        <v>5.3218000000000001E-2</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>28</v>
+      </c>
+      <c r="D78">
+        <v>4.0499999999999999E-7</v>
+      </c>
+      <c r="E78">
+        <v>5.4150000000000002E-7</v>
+      </c>
+      <c r="F78">
+        <v>4.2574399999999998E-2</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>6</v>
+      </c>
+      <c r="C79">
+        <v>28</v>
+      </c>
+      <c r="D79">
+        <v>4.8599999999999998E-7</v>
+      </c>
+      <c r="E79">
+        <v>6.4980000000000001E-7</v>
+      </c>
+      <c r="F79">
+        <v>3.5478666666666665E-2</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>28</v>
+      </c>
+      <c r="D80">
+        <v>5.6700000000000003E-7</v>
+      </c>
+      <c r="E80">
+        <v>7.5809999999999999E-7</v>
+      </c>
+      <c r="F80">
+        <v>3.0410285714285716E-2</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81">
+        <v>28</v>
+      </c>
+      <c r="D81">
+        <v>6.4799999999999998E-7</v>
+      </c>
+      <c r="E81">
+        <v>8.6639999999999998E-7</v>
+      </c>
+      <c r="F81">
+        <v>2.6609000000000001E-2</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82">
+        <v>7.2899999999999992E-7</v>
+      </c>
+      <c r="E82">
+        <v>9.7469999999999996E-7</v>
+      </c>
+      <c r="F82">
+        <v>2.3652444444444445E-2</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83">
+        <v>28</v>
+      </c>
+      <c r="D83">
+        <v>8.0999999999999997E-7</v>
+      </c>
+      <c r="E83">
+        <v>1.083E-6</v>
+      </c>
+      <c r="F83">
+        <v>2.1287199999999999E-2</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
         <v>29</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D84">
         <v>6.4200000000000006E-8</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E84">
         <v>8.72E-8</v>
       </c>
-      <c r="F21">
+      <c r="F84">
         <v>0.26840239999999999</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" t="str">
-        <f>CONCATENATE(B22,"x AWG ",C22)</f>
-        <v>1x AWG 30</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
+      <c r="G84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
         <v>30</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D85">
         <v>5.0899999999999999E-8</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E85">
         <v>7.0399999999999995E-8</v>
       </c>
-      <c r="F22">
+      <c r="F85">
         <v>0.33849600000000002</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="str">
-        <f>CONCATENATE(B23,"x AWG ",C23)</f>
-        <v>1x AWG 31</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+      <c r="G85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
         <v>31</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D86">
         <v>4.0399999999999998E-8</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E86">
         <v>5.6799999999999999E-8</v>
       </c>
-      <c r="F23">
+      <c r="F86">
         <v>0.426728</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="str">
-        <f>CONCATENATE(B24,"x AWG ",C24)</f>
-        <v>1x AWG 32</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+      <c r="G86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
         <v>32</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D87">
         <v>3.2000000000000002E-8</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E87">
         <v>4.5900000000000001E-8</v>
       </c>
-      <c r="F24">
+      <c r="F87">
         <v>0.53824799999999995</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
-        <f>CONCATENATE(B25,"x AWG ",C25)</f>
-        <v>1x AWG 33</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+      <c r="G87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
         <v>33</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D88">
         <v>2.5399999999999999E-8</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E88">
         <v>3.7100000000000001E-8</v>
       </c>
-      <c r="F25">
+      <c r="F88">
         <v>0.67863200000000001</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="str">
-        <f>CONCATENATE(B26,"x AWG ",C26)</f>
-        <v>1x AWG 34</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
+      <c r="G88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
         <v>34</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D89">
         <v>2.0100000000000001E-8</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E89">
         <v>2.9999999999999997E-8</v>
       </c>
-      <c r="F26">
+      <c r="F89">
         <v>0.85575199999999996</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" t="str">
-        <f>CONCATENATE(B27,"x AWG ",C27)</f>
-        <v>3x AWG 34</v>
-      </c>
-      <c r="B27">
+      <c r="G89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90">
         <v>3</v>
       </c>
-      <c r="C27">
+      <c r="C90">
         <v>34</v>
       </c>
-      <c r="D27">
+      <c r="D90">
         <v>6.0333659524529993E-8</v>
       </c>
-      <c r="E27">
+      <c r="E90">
         <v>9.9314665903109535E-8</v>
       </c>
-      <c r="F27">
+      <c r="F90">
         <v>0.28576115529000001</v>
       </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="str">
-        <f>CONCATENATE(B28,"x AWG ",C28)</f>
-        <v>4x AWG 34</v>
-      </c>
-      <c r="B28">
+      <c r="G90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91">
         <v>4</v>
       </c>
-      <c r="C28">
+      <c r="C91">
         <v>34</v>
       </c>
-      <c r="D28">
+      <c r="D91">
         <v>8.0444879366039995E-8</v>
       </c>
-      <c r="E28">
+      <c r="E91">
         <v>1.2971711464895944E-7</v>
       </c>
-      <c r="F28">
+      <c r="F91">
         <v>0.21433727066700001</v>
       </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="str">
-        <f>CONCATENATE(B29,"x AWG ",C29)</f>
-        <v>5x AWG 34</v>
-      </c>
-      <c r="B29">
+      <c r="G91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92">
         <v>5</v>
       </c>
-      <c r="C29">
+      <c r="C92">
         <v>34</v>
       </c>
-      <c r="D29">
+      <c r="D92">
         <v>1.0055609920755E-7</v>
       </c>
-      <c r="E29">
+      <c r="E92">
         <v>1.6417322322758922E-7</v>
       </c>
-      <c r="F29">
+      <c r="F92">
         <v>0.171456693174</v>
       </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="str">
-        <f>CONCATENATE(B30,"x AWG ",C30)</f>
-        <v>6x AWG 34</v>
-      </c>
-      <c r="B30">
+      <c r="G92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>35</v>
+      </c>
+      <c r="B93">
         <v>6</v>
       </c>
-      <c r="C30">
+      <c r="C93">
         <v>34</v>
       </c>
-      <c r="D30">
+      <c r="D93">
         <v>1.2066731904905999E-7</v>
       </c>
-      <c r="E30">
+      <c r="E93">
         <v>2.0268299163899907E-7</v>
       </c>
-      <c r="F30">
+      <c r="F93">
         <v>0.14288057764500001</v>
       </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="str">
-        <f>CONCATENATE(B31,"x AWG ",C31)</f>
-        <v>7x AWG 34</v>
-      </c>
-      <c r="B31">
+      <c r="G93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94">
         <v>7</v>
       </c>
-      <c r="C31">
+      <c r="C94">
         <v>34</v>
       </c>
-      <c r="D31">
+      <c r="D94">
         <v>1.4077853889057E-7</v>
       </c>
-      <c r="E31">
+      <c r="E94">
         <v>2.2345799828199655E-7</v>
       </c>
-      <c r="F31">
+      <c r="F94">
         <v>0.122473753467</v>
       </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" t="str">
-        <f>CONCATENATE(B32,"x AWG ",C32)</f>
-        <v>8x AWG 34</v>
-      </c>
-      <c r="B32">
+      <c r="G94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95">
         <v>8</v>
       </c>
-      <c r="C32">
+      <c r="C95">
         <v>34</v>
       </c>
-      <c r="D32">
+      <c r="D95">
         <v>1.6088975873207999E-7</v>
       </c>
-      <c r="E32">
+      <c r="E95">
         <v>2.680482564425763E-7</v>
       </c>
-      <c r="F32">
+      <c r="F95">
         <v>0.10715223113399999</v>
       </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" t="str">
-        <f>CONCATENATE(B33,"x AWG ",C33)</f>
-        <v>9x AWG 34</v>
-      </c>
-      <c r="B33">
+      <c r="G95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96">
         <v>9</v>
       </c>
-      <c r="C33">
+      <c r="C96">
         <v>34</v>
       </c>
-      <c r="D33">
+      <c r="D96">
         <v>1.8100097857358998E-7</v>
       </c>
-      <c r="E33">
+      <c r="E96">
         <v>2.9186350796015868E-7</v>
       </c>
-      <c r="F33">
+      <c r="F96">
         <v>9.5242782297000006E-2</v>
       </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" t="str">
-        <f>CONCATENATE(B34,"x AWG ",C34)</f>
-        <v>10x AWG 34</v>
-      </c>
-      <c r="B34">
+      <c r="G96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>39</v>
+      </c>
+      <c r="B97">
         <v>10</v>
       </c>
-      <c r="C34">
+      <c r="C97">
         <v>34</v>
       </c>
-      <c r="D34">
+      <c r="D97">
         <v>2.011121984151E-7</v>
       </c>
-      <c r="E34">
+      <c r="E97">
         <v>3.4253425586990836E-7</v>
       </c>
-      <c r="F34">
+      <c r="F97">
         <v>8.5728346587000001E-2</v>
       </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" t="str">
-        <f>CONCATENATE(B35,"x AWG ",C35)</f>
-        <v>15x AWG 34</v>
-      </c>
-      <c r="B35">
+      <c r="G97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98">
         <v>15</v>
       </c>
-      <c r="C35">
+      <c r="C98">
         <v>34</v>
       </c>
-      <c r="D35">
+      <c r="D98">
         <v>3.0166829762264999E-7</v>
       </c>
-      <c r="E35">
+      <c r="E98">
         <v>4.8694588741269527E-7</v>
       </c>
-      <c r="F35">
+      <c r="F98">
         <v>5.7152231058000005E-2</v>
       </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" t="str">
-        <f>CONCATENATE(B36,"x AWG ",C36)</f>
-        <v>20x AWG 34</v>
-      </c>
-      <c r="B36">
+      <c r="G98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>41</v>
+      </c>
+      <c r="B99">
         <v>20</v>
       </c>
-      <c r="C36">
+      <c r="C99">
         <v>34</v>
       </c>
-      <c r="D36">
+      <c r="D99">
         <v>4.0222439683019999E-7</v>
       </c>
-      <c r="E36">
+      <c r="E99">
         <v>6.5669289291035686E-7</v>
       </c>
-      <c r="F36">
+      <c r="F99">
         <v>4.2880577493000005E-2</v>
       </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" t="str">
-        <f>CONCATENATE(B37,"x AWG ",C37)</f>
-        <v>1x AWG 35</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
+      <c r="G99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>42</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
         <v>35</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D100">
         <v>1.6000000000000001E-8</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E100">
         <v>2.4299999999999999E-8</v>
       </c>
-      <c r="F37">
+      <c r="F100">
         <v>1.0791200000000001</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" t="str">
-        <f>CONCATENATE(B38,"x AWG ",C38)</f>
-        <v>1x AWG 36</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
+      <c r="G100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
         <v>36</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D101">
         <v>1.27E-8</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E101">
         <v>1.9700000000000001E-8</v>
       </c>
-      <c r="F38">
+      <c r="F101">
         <v>1.36</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" t="str">
-        <f>CONCATENATE(B39,"x AWG ",C39)</f>
-        <v>1x AWG 37</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
+      <c r="G101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>44</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
         <v>37</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D102">
         <v>1E-8</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E102">
         <v>1.6000000000000001E-8</v>
       </c>
-      <c r="F39">
+      <c r="F102">
         <v>1.7188760000000001</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" t="str">
-        <f>CONCATENATE(B40,"x AWG ",C40)</f>
-        <v>1x AWG 38</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
+      <c r="G102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>45</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
         <v>38</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D103">
         <v>8.0000000000000005E-9</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E103">
         <v>1.3000000000000001E-8</v>
       </c>
-      <c r="F40">
+      <c r="F103">
         <v>2.1658279999999999</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="str">
-        <f>CONCATENATE(B41,"x AWG ",C41)</f>
-        <v>2x AWG 38</v>
-      </c>
-      <c r="B41" s="1">
+      <c r="G103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>46</v>
+      </c>
+      <c r="B104">
         <v>2</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C104">
         <v>38</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D104">
         <v>1.6000000000000001E-8</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E104">
         <v>2.6000000000000001E-8</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F104">
         <v>1.0749999999999997</v>
       </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" t="str">
-        <f>CONCATENATE(B42,"x AWG ",C42)</f>
-        <v>3x AWG 38</v>
-      </c>
-      <c r="B42">
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>47</v>
+      </c>
+      <c r="B105">
         <v>3</v>
       </c>
-      <c r="C42">
+      <c r="C105">
         <v>38</v>
       </c>
-      <c r="D42">
+      <c r="D105">
         <v>2.4321958992E-8</v>
       </c>
-      <c r="E42">
+      <c r="E105">
         <v>4.1043305806897304E-8</v>
       </c>
-      <c r="F42">
+      <c r="F105">
         <v>0.70889107719300004</v>
       </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A43" t="str">
-        <f>CONCATENATE(B43,"x AWG ",C43)</f>
-        <v>4x AWG 38</v>
-      </c>
-      <c r="B43">
+      <c r="G105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106">
         <v>4</v>
       </c>
-      <c r="C43">
+      <c r="C106">
         <v>38</v>
       </c>
-      <c r="D43">
+      <c r="D106">
         <v>3.2429278656E-8</v>
       </c>
-      <c r="E43">
+      <c r="E106">
         <v>5.0670747909749768E-8</v>
       </c>
-      <c r="F43">
+      <c r="F106">
         <v>0.531660105795</v>
       </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" t="str">
-        <f>CONCATENATE(B44,"x AWG ",C44)</f>
-        <v>5x AWG 38</v>
-      </c>
-      <c r="B44">
+      <c r="G106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>49</v>
+      </c>
+      <c r="B107">
         <v>5</v>
       </c>
-      <c r="C44">
+      <c r="C107">
         <v>38</v>
       </c>
-      <c r="D44">
+      <c r="D107">
         <v>4.053659832E-8</v>
       </c>
-      <c r="E44">
+      <c r="E107">
         <v>7.296587699003967E-8</v>
       </c>
-      <c r="F44">
+      <c r="F107">
         <v>0.42532808463599997</v>
       </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" t="str">
-        <f>CONCATENATE(B45,"x AWG ",C45)</f>
-        <v>6x AWG 38</v>
-      </c>
-      <c r="B45">
+      <c r="G107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>50</v>
+      </c>
+      <c r="B108">
         <v>6</v>
       </c>
-      <c r="C45">
+      <c r="C108">
         <v>38</v>
       </c>
-      <c r="D45">
+      <c r="D108">
         <v>4.8643917984E-8</v>
       </c>
-      <c r="E45">
+      <c r="E108">
         <v>8.5633563967477089E-8</v>
       </c>
-      <c r="F45">
+      <c r="F108">
         <v>0.35442913439700002</v>
       </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" t="str">
-        <f>CONCATENATE(B46,"x AWG ",C46)</f>
-        <v>7x AWG 38</v>
-      </c>
-      <c r="B46">
+      <c r="G108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>51</v>
+      </c>
+      <c r="B109">
         <v>7</v>
       </c>
-      <c r="C46">
+      <c r="C109">
         <v>38</v>
       </c>
-      <c r="D46">
+      <c r="D109">
         <v>5.6751237648E-8</v>
       </c>
-      <c r="E46">
+      <c r="E109">
         <v>9.9314665903109535E-8</v>
       </c>
-      <c r="F46">
+      <c r="F109">
         <v>0.30380577473999998</v>
       </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="str">
-        <f>CONCATENATE(B47,"x AWG ",C47)</f>
-        <v>8x AWG 38</v>
-      </c>
-      <c r="B47">
+      <c r="G109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110">
         <v>8</v>
       </c>
-      <c r="C47">
+      <c r="C110">
         <v>38</v>
       </c>
-      <c r="D47">
+      <c r="D110">
         <v>6.4858557312E-8</v>
       </c>
-      <c r="E47">
+      <c r="E110">
         <v>1.1400918279693698E-7</v>
       </c>
-      <c r="F47">
+      <c r="F110">
         <v>0.265846457097</v>
       </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" t="str">
-        <f>CONCATENATE(B48,"x AWG ",C48)</f>
-        <v>9x AWG 38</v>
-      </c>
-      <c r="B48">
+      <c r="G110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>53</v>
+      </c>
+      <c r="B111">
         <v>9</v>
       </c>
-      <c r="C48">
+      <c r="C111">
         <v>38</v>
       </c>
-      <c r="D48">
+      <c r="D111">
         <v>7.2965876976000007E-8</v>
       </c>
-      <c r="E48">
+      <c r="E111">
         <v>1.2971711464895944E-7</v>
       </c>
-      <c r="F48">
+      <c r="F111">
         <v>0.23628608959799999</v>
       </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" t="str">
-        <f>CONCATENATE(B49,"x AWG ",C49)</f>
-        <v>10x AWG 38</v>
-      </c>
-      <c r="B49">
+      <c r="G111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>54</v>
+      </c>
+      <c r="B112">
         <v>10</v>
       </c>
-      <c r="C49">
+      <c r="C112">
         <v>38</v>
       </c>
-      <c r="D49">
+      <c r="D112">
         <v>8.107319664E-8</v>
       </c>
-      <c r="E49">
+      <c r="E112">
         <v>1.2971711464895944E-7</v>
       </c>
-      <c r="F49">
+      <c r="F112">
         <v>0.21266404231799999</v>
       </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" t="str">
-        <f>CONCATENATE(B50,"x AWG ",C50)</f>
-        <v>15x AWG 38</v>
-      </c>
-      <c r="B50">
+      <c r="G112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>55</v>
+      </c>
+      <c r="B113">
         <v>15</v>
       </c>
-      <c r="C50">
+      <c r="C113">
         <v>38</v>
       </c>
-      <c r="D50">
+      <c r="D113">
         <v>1.2160979495999999E-7</v>
       </c>
-      <c r="E50">
+      <c r="E113">
         <v>2.0268299163899907E-7</v>
       </c>
-      <c r="F50">
+      <c r="F113">
         <v>0.14176509207900001</v>
       </c>
-      <c r="G50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" t="str">
-        <f>CONCATENATE(B51,"x AWG ",C51)</f>
-        <v>20x AWG 38</v>
-      </c>
-      <c r="B51">
+      <c r="G113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>56</v>
+      </c>
+      <c r="B114">
         <v>20</v>
       </c>
-      <c r="C51">
+      <c r="C114">
         <v>38</v>
       </c>
-      <c r="D51">
+      <c r="D114">
         <v>1.6214639328E-7</v>
       </c>
-      <c r="E51">
+      <c r="E114">
         <v>2.680482564425763E-7</v>
       </c>
-      <c r="F51">
+      <c r="F114">
         <v>0.10633202115899999</v>
       </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" t="str">
-        <f>CONCATENATE(B52,"x AWG ",C52)</f>
-        <v>25x AWG 38</v>
-      </c>
-      <c r="B52">
+      <c r="G114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>57</v>
+      </c>
+      <c r="B115">
         <v>25</v>
       </c>
-      <c r="C52">
+      <c r="C115">
         <v>38</v>
       </c>
-      <c r="D52">
+      <c r="D115">
         <v>2.0268299160000001E-7</v>
       </c>
-      <c r="E52">
+      <c r="E115">
         <v>3.4253425586990836E-7</v>
       </c>
-      <c r="F52">
+      <c r="F115">
         <v>8.5072178607000004E-2</v>
       </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" t="str">
-        <f>CONCATENATE(B53,"x AWG ",C53)</f>
-        <v>30x AWG 38</v>
-      </c>
-      <c r="B53">
+      <c r="G115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>58</v>
+      </c>
+      <c r="B116">
         <v>30</v>
       </c>
-      <c r="C53">
+      <c r="C116">
         <v>38</v>
       </c>
-      <c r="D53">
+      <c r="D116">
         <v>2.4321958991999999E-7</v>
       </c>
-      <c r="E53">
+      <c r="E116">
         <v>4.2614098992099556E-7</v>
       </c>
-      <c r="F53">
+      <c r="F116">
         <v>7.0898950239000003E-2</v>
       </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" t="str">
-        <f>CONCATENATE(B54,"x AWG ",C54)</f>
-        <v>40x AWG 38</v>
-      </c>
-      <c r="B54">
+      <c r="G116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117">
         <v>40</v>
       </c>
-      <c r="C54">
+      <c r="C117">
         <v>38</v>
       </c>
-      <c r="D54">
+      <c r="D117">
         <v>3.2429278656E-7</v>
       </c>
-      <c r="E54">
+      <c r="E117">
         <v>5.5180444473717508E-7</v>
       </c>
-      <c r="F54">
+      <c r="F117">
         <v>5.3182414779000008E-2</v>
       </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" t="str">
-        <f>CONCATENATE(B55,"x AWG ",C55)</f>
-        <v>50x AWG 38</v>
-      </c>
-      <c r="B55">
+      <c r="G117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>60</v>
+      </c>
+      <c r="B118">
         <v>50</v>
       </c>
-      <c r="C55">
+      <c r="C118">
         <v>38</v>
       </c>
-      <c r="D55">
+      <c r="D118">
         <v>4.0536598320000001E-7</v>
       </c>
-      <c r="E55">
+      <c r="E118">
         <v>6.9368253888447434E-7</v>
       </c>
-      <c r="F55">
+      <c r="F118">
         <v>4.2519685104000005E-2</v>
       </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" t="str">
-        <f>CONCATENATE(B56,"x AWG ",C56)</f>
-        <v>60x AWG 38</v>
-      </c>
-      <c r="B56">
+      <c r="G118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>61</v>
+      </c>
+      <c r="B119">
         <v>60</v>
       </c>
-      <c r="C56">
+      <c r="C119">
         <v>38</v>
       </c>
-      <c r="D56">
+      <c r="D119">
         <v>4.8643917983999997E-7</v>
       </c>
-      <c r="E56">
+      <c r="E119">
         <v>8.1073196655599628E-7</v>
       </c>
-      <c r="F56">
+      <c r="F119">
         <v>3.5433070920000004E-2</v>
       </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" t="str">
-        <f>CONCATENATE(B57,"x AWG ",C57)</f>
-        <v>1x AWG 39</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57">
+      <c r="G119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
         <v>39</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D120">
         <v>6.3000000000000002E-9</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E120">
         <v>1.0600000000000001E-8</v>
       </c>
-      <c r="F57">
+      <c r="F120">
         <v>2.7320519999999999</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" t="str">
-        <f>CONCATENATE(B58,"x AWG ",C58)</f>
-        <v>1x AWG 40</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
+      <c r="G120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>63</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
         <v>40</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D121">
         <v>5.0000000000000001E-9</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E121">
         <v>8.5999999999999993E-9</v>
       </c>
-      <c r="F58">
+      <c r="F121">
         <v>3.4242699999999999</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" t="str">
-        <f>CONCATENATE(B59,"x AWG ",C59)</f>
-        <v>1x AWG 41</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
+      <c r="G121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>64</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
         <v>41</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D122">
         <v>4.0000000000000002E-9</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E122">
         <v>6.9999999999999998E-9</v>
       </c>
-      <c r="F59">
+      <c r="F122">
         <v>4.3123800000000001</v>
       </c>
-      <c r="G59">
+      <c r="G122">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DE9155-F280-4D61-95FD-A9B87D065F00}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>22</v>
+      </c>
+      <c r="D1">
+        <v>3.255E-7</v>
+      </c>
+      <c r="E1">
+        <v>4.0129999999999997E-7</v>
+      </c>
+      <c r="F1">
+        <v>5.2939199999999999E-2</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f t="shared" ref="A2:A11" si="0">CONCATENATE(B3,"x AWG ",C3)</f>
+        <v>2x AWG 22</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <f>$C$1</f>
+        <v>22</v>
+      </c>
+      <c r="D3" s="1">
+        <f>$D$1*B3</f>
+        <v>6.5099999999999999E-7</v>
+      </c>
+      <c r="E3" s="1">
+        <f>$E$1*B3</f>
+        <v>8.0259999999999995E-7</v>
+      </c>
+      <c r="F3">
+        <f>$F$1/B3</f>
+        <v>2.6469599999999999E-2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>3x AWG 22</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C11" si="1">$C$1</f>
+        <v>22</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D11" si="2">$D$1*B4</f>
+        <v>9.7649999999999988E-7</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E11" si="3">$E$1*B4</f>
+        <v>1.2039E-6</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F11" si="4">$F$1/B4</f>
+        <v>1.76464E-2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>4x AWG 22</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.302E-6</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="3"/>
+        <v>1.6051999999999999E-6</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="4"/>
+        <v>1.32348E-2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>5x AWG 22</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="2"/>
+        <v>1.6275000000000001E-6</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="3"/>
+        <v>2.0064999999999998E-6</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="4"/>
+        <v>1.0587839999999999E-2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>6x AWG 22</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="2"/>
+        <v>1.9529999999999998E-6</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="3"/>
+        <v>2.4078000000000001E-6</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="4"/>
+        <v>8.8231999999999998E-3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>7x AWG 22</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="2"/>
+        <v>2.2784999999999999E-6</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="3"/>
+        <v>2.8090999999999999E-6</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="4"/>
+        <v>7.5627428571428566E-3</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>8x AWG 22</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="2"/>
+        <v>2.604E-6</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="3"/>
+        <v>3.2103999999999998E-6</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>6.6173999999999998E-3</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>9x AWG 22</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="2"/>
+        <v>2.9295000000000001E-6</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="3"/>
+        <v>3.6116999999999997E-6</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="4"/>
+        <v>5.8821333333333335E-3</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>10x AWG 22</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="2"/>
+        <v>3.2550000000000002E-6</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="3"/>
+        <v>4.0129999999999995E-6</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>5.2939199999999997E-3</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>